--- a/reports/Korea_Petrochemical_NetZero_Report_v2.xlsx
+++ b/reports/Korea_Petrochemical_NetZero_Report_v2.xlsx
@@ -4946,7 +4946,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>$22.3</t>
+          <t>$18.8</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2,575</t>
+          <t>1,631</t>
         </is>
       </c>
     </row>
@@ -4974,11 +4974,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>$21.0</t>
+          <t>$17.1</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>157.1</v>
+        <v>133</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>$16.0</t>
+          <t>$12.2</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1,917</t>
+          <t>1,102</t>
         </is>
       </c>
     </row>
@@ -5030,11 +5030,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>$14.9</t>
+          <t>$10.9</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>115.3</v>
+        <v>85.7</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>$12.8</t>
+          <t>$10.6</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1,544</t>
+          <t>943</t>
         </is>
       </c>
     </row>
@@ -5086,11 +5086,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>$12.0</t>
+          <t>$9.5</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>92.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5259,20 +5259,20 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E19" t="n">
-        <v>36.4</v>
+        <v>27.9</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>$22.3</t>
+          <t>$18.8</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2,575</t>
+          <t>1,631</t>
         </is>
       </c>
     </row>
@@ -5296,24 +5296,24 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="D20" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E20" t="n">
-        <v>36.4</v>
+        <v>27.9</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>$21.0</t>
+          <t>$17.1</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>157.1</v>
+        <v>133</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -5333,20 +5333,20 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E21" t="n">
-        <v>25.2</v>
+        <v>18.6</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>$16.0</t>
+          <t>$12.2</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1,917</t>
+          <t>1,102</t>
         </is>
       </c>
     </row>
@@ -5370,24 +5370,24 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D22" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E22" t="n">
-        <v>25.2</v>
+        <v>18.6</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>$14.9</t>
+          <t>$10.9</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>115.3</v>
+        <v>85.7</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -5407,20 +5407,20 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E23" t="n">
-        <v>20.9</v>
+        <v>16.2</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>$12.8</t>
+          <t>$10.6</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1,544</t>
+          <t>943</t>
         </is>
       </c>
     </row>
@@ -5444,24 +5444,24 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>20.9</v>
+        <v>16.2</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>$12.0</t>
+          <t>$9.5</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>92.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>11.84469960238303</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -5842,10 +5842,10 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.6082413309331829</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>1.440571573262801</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -5857,16 +5857,16 @@
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>7.797193410933449</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>12.73680042842486</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>10.4125313632976</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -5877,7 +5877,7 @@
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>27.0641091201012</v>
+        <v>0</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -5889,10 +5889,10 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>1.389778576437629</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>3.291580838931226</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
@@ -5904,16 +5904,16 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>17.8159092579757</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>29.102481971471</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>23.79172916939707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -5924,7 +5924,7 @@
         <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>44.38016134744114</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -5936,10 +5936,10 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>2.278981258382113</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>5.397587190905004</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
@@ -5951,16 +5951,16 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>29.21481449515288</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>47.72271792776641</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>39.01406008181642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -5971,7 +5971,7 @@
         <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>264.1710655809483</v>
+        <v>0</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -5998,16 +5998,16 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>457.8445892152396</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>54.57543410248599</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>252.3685911896649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -6253,7 +6253,7 @@
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>124.7298567488214</v>
+        <v>0</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
@@ -6280,16 +6280,16 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>216.1739019390862</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>25.76809864713188</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>119.1572519789954</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -6300,7 +6300,7 @@
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>209.9990614169641</v>
+        <v>0</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -6327,16 +6327,16 @@
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>363.9570965071271</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>43.38397133971347</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>200.616850919699</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -6347,7 +6347,7 @@
         <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>211.8960966407574</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -6374,16 +6374,16 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>367.2449180210178</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>43.77588224266776</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>202.429131556161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -6394,7 +6394,7 @@
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>212.9768116178315</v>
+        <v>0</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -6421,16 +6421,16 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>369.1179448933935</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>43.99914851479024</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>203.4615630059944</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -6488,7 +6488,7 @@
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>342.2966472746527</v>
+        <v>425.2173739548368</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -6515,16 +6515,16 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>593.2469080842421</v>
+        <v>736.9598690810426</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>70.71549670194821</v>
+        <v>87.84619436072695</v>
       </c>
       <c r="O78" t="n">
-        <v>327.0037256036254</v>
+        <v>406.2197704292799</v>
       </c>
     </row>
     <row r="79">
@@ -6535,7 +6535,7 @@
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>477.0338185805047</v>
+        <v>488.6430988909878</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -6562,16 +6562,16 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>826.7648549225506</v>
+        <v>846.885325584804</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>98.55101910326376</v>
+        <v>100.9493949858334</v>
       </c>
       <c r="O79" t="n">
-        <v>455.7211914190439</v>
+        <v>466.8117993561374</v>
       </c>
     </row>
     <row r="80">
@@ -6582,7 +6582,7 @@
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>465.4926778083979</v>
+        <v>476.8210884339464</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -6609,16 +6609,16 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>806.7624794002346</v>
+        <v>826.3961644819435</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>96.16672025399173</v>
+        <v>98.5070709135952</v>
       </c>
       <c r="O80" t="n">
-        <v>444.6956787234239</v>
+        <v>455.5179655007458</v>
       </c>
     </row>
     <row r="81">
@@ -6629,7 +6629,7 @@
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>454.2145737253516</v>
+        <v>465.1832036592504</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -6656,16 +6656,16 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>787.215982437467</v>
+        <v>806.2261183707723</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>93.83676248654405</v>
+        <v>96.10278559863468</v>
       </c>
       <c r="O81" t="n">
-        <v>433.9214509234583</v>
+        <v>444.400031072315</v>
       </c>
     </row>
     <row r="82">
@@ -6676,7 +6676,7 @@
         <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>442.410396264181</v>
+        <v>453.1770675198673</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
@@ -6703,16 +6703,16 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>766.7577283555971</v>
+        <v>785.4178422762284</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>91.39812255544696</v>
+        <v>93.62242276911954</v>
       </c>
       <c r="O82" t="n">
-        <v>422.6446533321811</v>
+        <v>432.9302977899658</v>
       </c>
     </row>
     <row r="83">
@@ -6723,7 +6723,7 @@
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>427.4187226965541</v>
+        <v>437.9045242673123</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -6750,16 +6750,16 @@
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>740.7751075446288</v>
+        <v>758.9484358847278</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>88.30097377771556</v>
+        <v>90.4672487684235</v>
       </c>
       <c r="O83" t="n">
-        <v>408.3227686491742</v>
+        <v>418.3400919471935</v>
       </c>
     </row>
     <row r="84">
@@ -6770,7 +6770,7 @@
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>415.9700069100417</v>
+        <v>426.174938795866</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -6797,16 +6797,16 @@
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>720.9329171639737</v>
+        <v>738.6194599235289</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>85.93576912295592</v>
+        <v>88.04401889069776</v>
       </c>
       <c r="O84" t="n">
-        <v>397.385551631788</v>
+        <v>407.1345537700363</v>
       </c>
     </row>
     <row r="85">
@@ -6817,7 +6817,7 @@
         <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>404.5212911235247</v>
+        <v>414.4453533244197</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -6844,16 +6844,16 @@
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>701.0907267833103</v>
+        <v>718.2904839623301</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>83.57056446819522</v>
+        <v>85.62078901297211</v>
       </c>
       <c r="O85" t="n">
-        <v>386.4483346143973</v>
+        <v>395.9290155928789</v>
       </c>
     </row>
     <row r="86">
@@ -6864,7 +6864,7 @@
         <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>393.0725753370111</v>
+        <v>402.7157678529738</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -6891,16 +6891,16 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>681.2485364026521</v>
+        <v>697.9615080011317</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>81.20535981343522</v>
+        <v>83.19755913524646</v>
       </c>
       <c r="O86" t="n">
-        <v>375.5111175970099</v>
+        <v>384.7234774157218</v>
       </c>
     </row>
     <row r="87">
@@ -6911,7 +6911,7 @@
         <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>381.6238595504961</v>
+        <v>390.9861823815278</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
@@ -6938,16 +6938,16 @@
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>661.4063460219927</v>
+        <v>677.6325320399339</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>78.84015515867499</v>
+        <v>80.77432925752075</v>
       </c>
       <c r="O87" t="n">
-        <v>364.5739005796212</v>
+        <v>373.5179392385645</v>
       </c>
     </row>
     <row r="108">
@@ -7136,7 +7136,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C113" t="n">
-        <v>6.479858043890045</v>
+        <v>6.406616217891267</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -7148,10 +7148,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G113" t="n">
-        <v>0.0271310869224834</v>
+        <v>0.0233700201820057</v>
       </c>
       <c r="H113" t="n">
-        <v>0.06678550964040179</v>
+        <v>0.0578777199919018</v>
       </c>
       <c r="I113" t="n">
         <v>0.001730378942303</v>
@@ -7163,16 +7163,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L113" t="n">
-        <v>9.280588291719214</v>
+        <v>9.23237426331384</v>
       </c>
       <c r="M113" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N113" t="n">
-        <v>3.189352156877229</v>
+        <v>3.110594015930187</v>
       </c>
       <c r="O113" t="n">
-        <v>5.338587462711132</v>
+        <v>5.274201464254571</v>
       </c>
     </row>
     <row r="114">
@@ -7183,7 +7183,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C114" t="n">
-        <v>6.652726323297285</v>
+        <v>6.406616217891267</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
@@ -7195,10 +7195,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G114" t="n">
-        <v>0.0360081066758282</v>
+        <v>0.0233700201820057</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0878100301088499</v>
+        <v>0.0578777199919018</v>
       </c>
       <c r="I114" t="n">
         <v>0.001730378942303</v>
@@ -7210,16 +7210,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L114" t="n">
-        <v>9.394384964864251</v>
+        <v>9.23237426331384</v>
       </c>
       <c r="M114" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N114" t="n">
-        <v>3.375240262876323</v>
+        <v>3.110594015930187</v>
       </c>
       <c r="O114" t="n">
-        <v>5.49055386468599</v>
+        <v>5.274201464254571</v>
       </c>
     </row>
     <row r="115">
@@ -7230,7 +7230,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C115" t="n">
-        <v>6.945862332197287</v>
+        <v>6.406616217891267</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
@@ -7242,10 +7242,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0510610368625851</v>
+        <v>0.0233700201820057</v>
       </c>
       <c r="H115" t="n">
-        <v>0.1234617068669583</v>
+        <v>0.0578777199919018</v>
       </c>
       <c r="I115" t="n">
         <v>0.001730378942303</v>
@@ -7257,16 +7257,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L115" t="n">
-        <v>9.587352134470018</v>
+        <v>9.23237426331384</v>
       </c>
       <c r="M115" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N115" t="n">
-        <v>3.690454237825348</v>
+        <v>3.110594015930187</v>
       </c>
       <c r="O115" t="n">
-        <v>5.748246164942306</v>
+        <v>5.274201464254571</v>
       </c>
     </row>
     <row r="116">
@@ -7277,7 +7277,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C116" t="n">
-        <v>8.318515908255156</v>
+        <v>6.406616217891267</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -7289,10 +7289,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G116" t="n">
-        <v>0.0510610368625851</v>
+        <v>0.0233700201820057</v>
       </c>
       <c r="H116" t="n">
-        <v>0.1234617068669583</v>
+        <v>0.0578777199919018</v>
       </c>
       <c r="I116" t="n">
         <v>0.001730378942303</v>
@@ -7304,16 +7304,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L116" t="n">
-        <v>11.96634852941195</v>
+        <v>9.23237426331384</v>
       </c>
       <c r="M116" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N116" t="n">
-        <v>3.974032473848069</v>
+        <v>3.110594015930187</v>
       </c>
       <c r="O116" t="n">
-        <v>7.0595731583788</v>
+        <v>5.274201464254571</v>
       </c>
     </row>
     <row r="117">
@@ -7324,7 +7324,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C117" t="n">
-        <v>8.318515908255156</v>
+        <v>6.406616217891267</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -7336,10 +7336,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0510610368625851</v>
+        <v>0.0233700201820057</v>
       </c>
       <c r="H117" t="n">
-        <v>0.1234617068669583</v>
+        <v>0.0578777199919018</v>
       </c>
       <c r="I117" t="n">
         <v>0.001730378942303</v>
@@ -7351,16 +7351,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L117" t="n">
-        <v>11.96634852941195</v>
+        <v>9.23237426331384</v>
       </c>
       <c r="M117" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N117" t="n">
-        <v>3.974032473848069</v>
+        <v>3.110594015930187</v>
       </c>
       <c r="O117" t="n">
-        <v>7.0595731583788</v>
+        <v>5.274201464254571</v>
       </c>
     </row>
     <row r="118">
@@ -7371,7 +7371,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C118" t="n">
-        <v>8.318515908255156</v>
+        <v>6.406616217891267</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -7383,10 +7383,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G118" t="n">
-        <v>0.0510610368625851</v>
+        <v>0.0233700201820057</v>
       </c>
       <c r="H118" t="n">
-        <v>0.1234617068669583</v>
+        <v>0.0578777199919018</v>
       </c>
       <c r="I118" t="n">
         <v>0.001730378942303</v>
@@ -7398,16 +7398,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L118" t="n">
-        <v>11.96634852941195</v>
+        <v>9.23237426331384</v>
       </c>
       <c r="M118" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N118" t="n">
-        <v>3.974032473848069</v>
+        <v>3.110594015930187</v>
       </c>
       <c r="O118" t="n">
-        <v>7.0595731583788</v>
+        <v>5.274201464254571</v>
       </c>
     </row>
     <row r="119">
@@ -7418,7 +7418,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C119" t="n">
-        <v>8.318515908255156</v>
+        <v>6.406616217891267</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
@@ -7430,10 +7430,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0510610368625851</v>
+        <v>0.0233700201820057</v>
       </c>
       <c r="H119" t="n">
-        <v>0.1234617068669583</v>
+        <v>0.0578777199919018</v>
       </c>
       <c r="I119" t="n">
         <v>0.001730378942303</v>
@@ -7445,16 +7445,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L119" t="n">
-        <v>11.96634852941195</v>
+        <v>9.23237426331384</v>
       </c>
       <c r="M119" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N119" t="n">
-        <v>3.974032473848069</v>
+        <v>3.110594015930187</v>
       </c>
       <c r="O119" t="n">
-        <v>7.0595731583788</v>
+        <v>5.274201464254571</v>
       </c>
     </row>
     <row r="120">
@@ -7465,7 +7465,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C120" t="n">
-        <v>8.318515908255156</v>
+        <v>6.406616217891267</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
@@ -7477,10 +7477,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0510610368625851</v>
+        <v>0.0233700201820057</v>
       </c>
       <c r="H120" t="n">
-        <v>0.1234617068669583</v>
+        <v>0.0578777199919018</v>
       </c>
       <c r="I120" t="n">
         <v>0.001730378942303</v>
@@ -7492,16 +7492,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L120" t="n">
-        <v>11.96634852941195</v>
+        <v>9.23237426331384</v>
       </c>
       <c r="M120" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N120" t="n">
-        <v>3.974032473848069</v>
+        <v>3.110594015930187</v>
       </c>
       <c r="O120" t="n">
-        <v>7.0595731583788</v>
+        <v>5.274201464254571</v>
       </c>
     </row>
     <row r="121">
@@ -7512,7 +7512,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C121" t="n">
-        <v>8.318515908255156</v>
+        <v>6.406616217891267</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -7524,10 +7524,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G121" t="n">
-        <v>0.0510610368625851</v>
+        <v>0.0233700201820057</v>
       </c>
       <c r="H121" t="n">
-        <v>0.1234617068669583</v>
+        <v>0.0578777199919018</v>
       </c>
       <c r="I121" t="n">
         <v>0.001730378942303</v>
@@ -7539,16 +7539,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L121" t="n">
-        <v>11.96634852941195</v>
+        <v>9.23237426331384</v>
       </c>
       <c r="M121" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N121" t="n">
-        <v>3.974032473848069</v>
+        <v>3.110594015930187</v>
       </c>
       <c r="O121" t="n">
-        <v>7.0595731583788</v>
+        <v>5.274201464254571</v>
       </c>
     </row>
     <row r="122">
@@ -7559,7 +7559,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C122" t="n">
-        <v>9.07316001872177</v>
+        <v>6.406616217891267</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -7571,10 +7571,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0510610368625851</v>
+        <v>0.0233700201820057</v>
       </c>
       <c r="H122" t="n">
-        <v>0.1234617068669583</v>
+        <v>0.0578777199919018</v>
       </c>
       <c r="I122" t="n">
         <v>0.001730378942303</v>
@@ -7586,16 +7586,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L122" t="n">
-        <v>13.27424999091555</v>
+        <v>9.23237426331384</v>
       </c>
       <c r="M122" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N122" t="n">
-        <v>4.129935353790762</v>
+        <v>3.110594015930187</v>
       </c>
       <c r="O122" t="n">
-        <v>7.780501737703772</v>
+        <v>5.274201464254571</v>
       </c>
     </row>
     <row r="123">
@@ -7606,7 +7606,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C123" t="n">
-        <v>10.37949220828739</v>
+        <v>6.406616217891267</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
@@ -7618,10 +7618,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G123" t="n">
-        <v>0.0510610368625851</v>
+        <v>0.0233700201820057</v>
       </c>
       <c r="H123" t="n">
-        <v>0.1234617068669583</v>
+        <v>0.0578777199919018</v>
       </c>
       <c r="I123" t="n">
         <v>0.001730378942303</v>
@@ -7633,16 +7633,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L123" t="n">
-        <v>15.5383023518167</v>
+        <v>9.23237426331384</v>
       </c>
       <c r="M123" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N123" t="n">
-        <v>4.399812170810106</v>
+        <v>3.110594015930187</v>
       </c>
       <c r="O123" t="n">
-        <v>9.02847041126528</v>
+        <v>5.274201464254571</v>
       </c>
     </row>
     <row r="124">
@@ -7653,7 +7653,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C124" t="n">
-        <v>11.73583195731639</v>
+        <v>6.406616217891267</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -7665,10 +7665,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0510610368625851</v>
+        <v>0.0233700201820057</v>
       </c>
       <c r="H124" t="n">
-        <v>0.1234617068669583</v>
+        <v>0.0578777199919018</v>
       </c>
       <c r="I124" t="n">
         <v>0.001730378942303</v>
@@ -7680,16 +7680,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L124" t="n">
-        <v>17.88902465315896</v>
+        <v>9.23237426331384</v>
       </c>
       <c r="M124" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N124" t="n">
-        <v>4.680020112701579</v>
+        <v>3.110594015930187</v>
       </c>
       <c r="O124" t="n">
-        <v>10.3242124369267</v>
+        <v>5.274201464254571</v>
       </c>
     </row>
     <row r="125">
@@ -7700,7 +7700,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C125" t="n">
-        <v>13.13978357619016</v>
+        <v>6.406616217891267</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -7712,10 +7712,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G125" t="n">
-        <v>0.0510610368625851</v>
+        <v>0.0233700201820057</v>
       </c>
       <c r="H125" t="n">
-        <v>0.1234617068669583</v>
+        <v>0.0578777199919018</v>
       </c>
       <c r="I125" t="n">
         <v>0.001730378942303</v>
@@ -7727,16 +7727,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L125" t="n">
-        <v>20.3222648371577</v>
+        <v>9.23237426331384</v>
       </c>
       <c r="M125" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N125" t="n">
-        <v>4.970064250920967</v>
+        <v>3.110594015930187</v>
       </c>
       <c r="O125" t="n">
-        <v>11.66543915823487</v>
+        <v>5.274201464254571</v>
       </c>
     </row>
     <row r="126">
@@ -7747,7 +7747,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C126" t="n">
-        <v>13.13978357619016</v>
+        <v>6.406616217891267</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -7759,10 +7759,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G126" t="n">
-        <v>0.0510610368625851</v>
+        <v>0.0233700201820057</v>
       </c>
       <c r="H126" t="n">
-        <v>0.1234617068669583</v>
+        <v>0.0578777199919018</v>
       </c>
       <c r="I126" t="n">
         <v>0.001730378942303</v>
@@ -7774,16 +7774,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L126" t="n">
-        <v>20.3222648371577</v>
+        <v>9.23237426331384</v>
       </c>
       <c r="M126" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N126" t="n">
-        <v>4.970064250920967</v>
+        <v>3.110594015930187</v>
       </c>
       <c r="O126" t="n">
-        <v>11.66543915823487</v>
+        <v>5.274201464254571</v>
       </c>
     </row>
     <row r="127">
@@ -7794,7 +7794,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C127" t="n">
-        <v>15.52058702836294</v>
+        <v>9.364164881881599</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -7806,10 +7806,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0510610368625851</v>
+        <v>0.0233700201820057</v>
       </c>
       <c r="H127" t="n">
-        <v>0.1234617068669583</v>
+        <v>0.0578777199919018</v>
       </c>
       <c r="I127" t="n">
         <v>0.001730378942303</v>
@@ -7821,16 +7821,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L127" t="n">
-        <v>24.44852285926594</v>
+        <v>14.35821062306387</v>
       </c>
       <c r="M127" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N127" t="n">
-        <v>5.461917443204859</v>
+        <v>3.721597729987737</v>
       </c>
       <c r="O127" t="n">
-        <v>13.93987452004486</v>
+        <v>8.099614565665572</v>
       </c>
     </row>
     <row r="128">
@@ -7841,7 +7841,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C128" t="n">
-        <v>18.9188118112617</v>
+        <v>12.84509018312116</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -7853,10 +7853,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G128" t="n">
-        <v>0.0510610368625851</v>
+        <v>0.0233700201820057</v>
       </c>
       <c r="H128" t="n">
-        <v>0.1234617068669583</v>
+        <v>0.0578777199919018</v>
       </c>
       <c r="I128" t="n">
         <v>0.001730378942303</v>
@@ -7868,16 +7868,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L128" t="n">
-        <v>30.33811120750454</v>
+        <v>20.39113028112767</v>
       </c>
       <c r="M128" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N128" t="n">
-        <v>6.163960993268431</v>
+        <v>4.44072648459112</v>
       </c>
       <c r="O128" t="n">
-        <v>17.18627548042246</v>
+        <v>11.42502120086386</v>
       </c>
     </row>
     <row r="129">
@@ -7888,7 +7888,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C129" t="n">
-        <v>22.31703659416047</v>
+        <v>16.32601548436072</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -7900,10 +7900,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G129" t="n">
-        <v>0.0510610368625851</v>
+        <v>0.0233700201820057</v>
       </c>
       <c r="H129" t="n">
-        <v>0.1234617068669583</v>
+        <v>0.0578777199919018</v>
       </c>
       <c r="I129" t="n">
         <v>0.001730378942303</v>
@@ -7915,16 +7915,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L129" t="n">
-        <v>36.22769955574316</v>
+        <v>26.42404993919144</v>
       </c>
       <c r="M129" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N129" t="n">
-        <v>6.866004543332007</v>
+        <v>5.159855239194501</v>
       </c>
       <c r="O129" t="n">
-        <v>20.43267644080007</v>
+        <v>14.75042783606215</v>
       </c>
     </row>
     <row r="130">
@@ -7935,7 +7935,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C130" t="n">
-        <v>25.71723043701974</v>
+        <v>19.80831912757262</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
@@ -7947,10 +7947,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0510610368625851</v>
+        <v>0.0233700201820057</v>
       </c>
       <c r="H130" t="n">
-        <v>0.1234617068669583</v>
+        <v>0.0578777199919018</v>
       </c>
       <c r="I130" t="n">
         <v>0.001730378942303</v>
@@ -7962,16 +7962,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L130" t="n">
-        <v>42.12070055421573</v>
+        <v>32.45935845241897</v>
       </c>
       <c r="M130" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N130" t="n">
-        <v>7.568454883979865</v>
+        <v>5.879268747206878</v>
       </c>
       <c r="O130" t="n">
-        <v>23.68095848867342</v>
+        <v>18.07715123250744</v>
       </c>
     </row>
     <row r="131">
@@ -7982,7 +7982,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C131" t="n">
-        <v>29.11545521991852</v>
+        <v>23.28924442881218</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -7994,10 +7994,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G131" t="n">
-        <v>0.0510610368625851</v>
+        <v>0.0233700201820057</v>
       </c>
       <c r="H131" t="n">
-        <v>0.1234617068669583</v>
+        <v>0.0578777199919018</v>
       </c>
       <c r="I131" t="n">
         <v>0.001730378942303</v>
@@ -8009,16 +8009,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L131" t="n">
-        <v>48.01028890245438</v>
+        <v>38.49227811048275</v>
       </c>
       <c r="M131" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N131" t="n">
-        <v>8.270498434043443</v>
+        <v>6.598397501810261</v>
       </c>
       <c r="O131" t="n">
-        <v>26.92735944905104</v>
+        <v>21.40255786770573</v>
       </c>
     </row>
     <row r="132">
@@ -8029,7 +8029,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C132" t="n">
-        <v>32.48646597928123</v>
+        <v>26.74295570651569</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -8041,10 +8041,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G132" t="n">
-        <v>0.0510610368625851</v>
+        <v>0.0233700201820057</v>
       </c>
       <c r="H132" t="n">
-        <v>0.1234617068669583</v>
+        <v>0.0578777199919018</v>
       </c>
       <c r="I132" t="n">
         <v>0.001730378942303</v>
@@ -8056,16 +8056,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L132" t="n">
-        <v>53.85271162564862</v>
+        <v>44.47803214350218</v>
       </c>
       <c r="M132" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N132" t="n">
-        <v>8.966919804611736</v>
+        <v>7.311904076918363</v>
       </c>
       <c r="O132" t="n">
-        <v>30.14776223750435</v>
+        <v>24.70196633097972</v>
       </c>
     </row>
     <row r="133">
@@ -8076,7 +8076,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C133" t="n">
-        <v>35.85747673864395</v>
+        <v>30.19666698421919</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -8088,10 +8088,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G133" t="n">
-        <v>0.0510610368625851</v>
+        <v>0.0233700201820057</v>
       </c>
       <c r="H133" t="n">
-        <v>0.1234617068669583</v>
+        <v>0.0578777199919018</v>
       </c>
       <c r="I133" t="n">
         <v>0.001730378942303</v>
@@ -8103,16 +8103,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L133" t="n">
-        <v>59.6951343488429</v>
+        <v>50.46378617652161</v>
       </c>
       <c r="M133" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N133" t="n">
-        <v>9.663341175180031</v>
+        <v>8.025410652026466</v>
       </c>
       <c r="O133" t="n">
-        <v>33.36816502595767</v>
+        <v>28.00137479425372</v>
       </c>
     </row>
     <row r="134">
@@ -8123,7 +8123,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C134" t="n">
-        <v>39.22848749800666</v>
+        <v>33.65037826192269</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G134" t="n">
-        <v>0.0510610368625851</v>
+        <v>0.0233700201820057</v>
       </c>
       <c r="H134" t="n">
-        <v>0.1234617068669583</v>
+        <v>0.0578777199919018</v>
       </c>
       <c r="I134" t="n">
         <v>0.001730378942303</v>
@@ -8150,16 +8150,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L134" t="n">
-        <v>65.53755707203715</v>
+        <v>56.44954020954102</v>
       </c>
       <c r="M134" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N134" t="n">
-        <v>10.35976254574833</v>
+        <v>8.738917227134564</v>
       </c>
       <c r="O134" t="n">
-        <v>36.58856781441099</v>
+        <v>31.30078325752771</v>
       </c>
     </row>
     <row r="135">
@@ -8170,7 +8170,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C135" t="n">
-        <v>42.59949825736937</v>
+        <v>37.10408953962619</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -8182,10 +8182,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G135" t="n">
-        <v>0.0510610368625851</v>
+        <v>0.0233700201820057</v>
       </c>
       <c r="H135" t="n">
-        <v>0.1234617068669583</v>
+        <v>0.0578777199919018</v>
       </c>
       <c r="I135" t="n">
         <v>0.001730378942303</v>
@@ -8197,16 +8197,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L135" t="n">
-        <v>71.37997979523142</v>
+        <v>62.43529424256044</v>
       </c>
       <c r="M135" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N135" t="n">
-        <v>11.05618391631662</v>
+        <v>9.452423802242665</v>
       </c>
       <c r="O135" t="n">
-        <v>39.80897060286431</v>
+        <v>34.6001917208017</v>
       </c>
     </row>
     <row r="136">
@@ -8217,7 +8217,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C136" t="n">
-        <v>45.97050901673209</v>
+        <v>40.55780081732968</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
@@ -8229,10 +8229,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0510610368625851</v>
+        <v>0.0233700201820057</v>
       </c>
       <c r="H136" t="n">
-        <v>0.1234617068669583</v>
+        <v>0.0578777199919018</v>
       </c>
       <c r="I136" t="n">
         <v>0.001730378942303</v>
@@ -8244,16 +8244,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L136" t="n">
-        <v>77.2224025184257</v>
+        <v>68.42104827557986</v>
       </c>
       <c r="M136" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N136" t="n">
-        <v>11.75260528688492</v>
+        <v>10.16593037735076</v>
       </c>
       <c r="O136" t="n">
-        <v>43.02937339131763</v>
+        <v>37.89960018407569</v>
       </c>
     </row>
   </sheetData>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>36.37</t>
+          <t>27.89</t>
         </is>
       </c>
     </row>
@@ -25678,7 +25678,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$22.3</t>
+          <t>$18.8</t>
         </is>
       </c>
     </row>
@@ -27971,7 +27971,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>36.37</t>
+          <t>27.89</t>
         </is>
       </c>
     </row>
@@ -27995,7 +27995,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$21.0</t>
+          <t>$17.1</t>
         </is>
       </c>
     </row>
@@ -30288,7 +30288,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>18.64</t>
         </is>
       </c>
     </row>
@@ -30312,7 +30312,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$16.0</t>
+          <t>$12.2</t>
         </is>
       </c>
     </row>
@@ -32202,7 +32202,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>18.64</t>
         </is>
       </c>
     </row>
@@ -32226,7 +32226,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$14.9</t>
+          <t>$10.9</t>
         </is>
       </c>
     </row>
@@ -34116,7 +34116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>16.22</t>
         </is>
       </c>
     </row>
@@ -34140,7 +34140,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$12.8</t>
+          <t>$10.6</t>
         </is>
       </c>
     </row>
@@ -35782,7 +35782,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>16.22</t>
         </is>
       </c>
     </row>
@@ -35806,7 +35806,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$12.0</t>
+          <t>$9.5</t>
         </is>
       </c>
     </row>

--- a/reports/Korea_Petrochemical_NetZero_Report_v2.xlsx
+++ b/reports/Korea_Petrochemical_NetZero_Report_v2.xlsx
@@ -4946,7 +4946,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>$18.8</t>
+          <t>$15.1</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1,631</t>
+          <t>1,179</t>
         </is>
       </c>
     </row>
@@ -4974,11 +4974,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>$17.1</t>
+          <t>$14.4</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>133</v>
+        <v>106.3</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>$12.2</t>
+          <t>$12.0</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1,102</t>
+          <t>1,049</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>$10.9</t>
+          <t>$11.0</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>$10.6</t>
+          <t>$10.3</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>895</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>$9.5</t>
+          <t>$9.4</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>$18.8</t>
+          <t>$15.1</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1,631</t>
+          <t>1,179</t>
         </is>
       </c>
     </row>
@@ -5309,11 +5309,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>$17.1</t>
+          <t>$14.4</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>133</v>
+        <v>106.3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>$12.2</t>
+          <t>$12.0</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1,102</t>
+          <t>1,049</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>$10.9</t>
+          <t>$11.0</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>$10.6</t>
+          <t>$10.3</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>895</t>
         </is>
       </c>
     </row>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>$9.5</t>
+          <t>$9.4</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -5830,7 +5830,7 @@
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>5.907559139082105</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -5842,10 +5842,10 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>0.3033611449798918</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>0.7184869223207967</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -5857,16 +5857,16 @@
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>3.888860227800406</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>6.352495571814071</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>5.193263390474846</v>
       </c>
     </row>
     <row r="65">
@@ -5877,7 +5877,7 @@
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>17.79104934675205</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -5889,10 +5889,10 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>0.9135944259142944</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>2.163776271902276</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
@@ -5904,16 +5904,16 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>11.71158892980096</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>19.1310081765391</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>15.63989510310253</v>
       </c>
     </row>
     <row r="66">
@@ -5924,7 +5924,7 @@
         <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>29.95032415986638</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -5936,10 +5936,10 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1.537989619020166</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>3.642606992416182</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
@@ -5951,16 +5951,16 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>19.71586262497087</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>32.20607650649927</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>26.32896570823929</v>
       </c>
     </row>
     <row r="67">
@@ -5971,7 +5971,7 @@
         <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>183.3485211515685</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -5998,16 +5998,16 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>317.7680650424555</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>37.87820256503265</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>175.1569873028019</v>
       </c>
     </row>
     <row r="68">
@@ -6253,7 +6253,7 @@
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>95.40732846222774</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
@@ -6280,16 +6280,16 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>165.3539497667921</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>19.71032049226839</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>91.1447777985512</v>
       </c>
     </row>
     <row r="74">
@@ -6300,7 +6300,7 @@
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>146.1243864615807</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -6327,16 +6327,16 @@
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>253.2535482139352</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>30.18802156308265</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>139.5959298898433</v>
       </c>
     </row>
     <row r="75">
@@ -6347,7 +6347,7 @@
         <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>147.476957781063</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -6374,16 +6374,16 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>255.5977393114381</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>30.46745098035433</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>140.8880718495641</v>
       </c>
     </row>
     <row r="76">
@@ -6394,7 +6394,7 @@
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>148.2581049278401</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -6421,16 +6421,16 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>256.9515741598772</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>30.62882915604333</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>141.6343193786431</v>
       </c>
     </row>
     <row r="77">
@@ -6488,7 +6488,7 @@
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>425.2173739548368</v>
+        <v>236.8687926858151</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -6515,16 +6515,16 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>736.9598690810426</v>
+        <v>410.526015961106</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>87.84619436072695</v>
+        <v>48.93502306064972</v>
       </c>
       <c r="O78" t="n">
-        <v>406.2197704292799</v>
+        <v>226.2861126575518</v>
       </c>
     </row>
     <row r="79">
@@ -6535,7 +6535,7 @@
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>488.6430988909878</v>
+        <v>332.0135566374098</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -6562,16 +6562,16 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>846.885325584804</v>
+        <v>575.4249055181479</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>100.9493949858334</v>
+        <v>68.5911000190315</v>
       </c>
       <c r="O79" t="n">
-        <v>466.8117993561374</v>
+        <v>317.1800566431751</v>
       </c>
     </row>
     <row r="80">
@@ -6582,7 +6582,7 @@
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>476.8210884339464</v>
+        <v>323.9809705897288</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -6609,16 +6609,16 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>826.3961644819435</v>
+        <v>561.5033352233509</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>98.5070709135952</v>
+        <v>66.93163792179651</v>
       </c>
       <c r="O80" t="n">
-        <v>455.5179655007458</v>
+        <v>309.5063455953547</v>
       </c>
     </row>
     <row r="81">
@@ -6629,7 +6629,7 @@
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>465.1832036592504</v>
+        <v>316.1325102243933</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -6656,16 +6656,16 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>806.2261183707723</v>
+        <v>547.9008799202431</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>96.10278559863468</v>
+        <v>65.31021458183922</v>
       </c>
       <c r="O81" t="n">
-        <v>444.400031072315</v>
+        <v>302.0085339744953</v>
       </c>
     </row>
     <row r="82">
@@ -6676,7 +6676,7 @@
         <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>453.1770675198673</v>
+        <v>307.9157984943717</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
@@ -6703,16 +6703,16 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>785.4178422762284</v>
+        <v>533.6601946337656</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>93.62242276911954</v>
+        <v>63.61271372732751</v>
       </c>
       <c r="O82" t="n">
-        <v>432.9302977899658</v>
+        <v>294.1589234997186</v>
       </c>
     </row>
     <row r="83">
@@ -6723,7 +6723,7 @@
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>437.9045242673123</v>
+        <v>299.8832124466924</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -6750,16 +6750,16 @@
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>758.9484358847278</v>
+        <v>519.7386243389715</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>90.4672487684235</v>
+        <v>61.95325163009293</v>
       </c>
       <c r="O83" t="n">
-        <v>418.3400919471935</v>
+        <v>286.4852124518998</v>
       </c>
     </row>
     <row r="84">
@@ -6770,7 +6770,7 @@
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>426.174938795866</v>
+        <v>291.8506263990124</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -6797,16 +6797,16 @@
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>738.6194599235289</v>
+        <v>505.8170540441763</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>88.04401889069776</v>
+        <v>60.29378953285811</v>
       </c>
       <c r="O84" t="n">
-        <v>407.1345537700363</v>
+        <v>278.8115014040803</v>
       </c>
     </row>
     <row r="85">
@@ -6817,7 +6817,7 @@
         <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>414.4453533244197</v>
+        <v>283.8180403513331</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -6844,16 +6844,16 @@
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>718.2904839623301</v>
+        <v>491.8954837493825</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>85.62078901297211</v>
+        <v>58.63432743562347</v>
       </c>
       <c r="O85" t="n">
-        <v>395.9290155928789</v>
+        <v>271.1377903562616</v>
       </c>
     </row>
     <row r="86">
@@ -6864,7 +6864,7 @@
         <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>402.7157678529738</v>
+        <v>275.7854543036546</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -6891,16 +6891,16 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>697.9615080011317</v>
+        <v>477.9739134545902</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>83.19755913524646</v>
+        <v>56.97486533838903</v>
       </c>
       <c r="O86" t="n">
-        <v>384.7234774157218</v>
+        <v>263.4640793084437</v>
       </c>
     </row>
     <row r="87">
@@ -6911,7 +6911,7 @@
         <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>390.9861823815278</v>
+        <v>267.7528682559746</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
@@ -6938,16 +6938,16 @@
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>677.6325320399339</v>
+        <v>464.0523431597945</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>80.77432925752075</v>
+        <v>55.31540324115422</v>
       </c>
       <c r="O87" t="n">
-        <v>373.5179392385645</v>
+        <v>255.7903682606241</v>
       </c>
     </row>
     <row r="108">
@@ -7136,7 +7136,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C113" t="n">
-        <v>6.406616217891267</v>
+        <v>6.443145672674155</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -7148,10 +7148,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G113" t="n">
-        <v>0.0233700201820057</v>
+        <v>0.025245857049235</v>
       </c>
       <c r="H113" t="n">
-        <v>0.0578777199919018</v>
+        <v>0.0623204915195503</v>
       </c>
       <c r="I113" t="n">
         <v>0.001730378942303</v>
@@ -7163,16 +7163,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L113" t="n">
-        <v>9.23237426331384</v>
+        <v>9.256421071903301</v>
       </c>
       <c r="M113" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N113" t="n">
-        <v>3.110594015930187</v>
+        <v>3.14987473987824</v>
       </c>
       <c r="O113" t="n">
-        <v>5.274201464254571</v>
+        <v>5.306314063677055</v>
       </c>
     </row>
     <row r="114">
@@ -7183,7 +7183,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C114" t="n">
-        <v>6.406616217891267</v>
+        <v>6.556783556551074</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
@@ -7195,10 +7195,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G114" t="n">
-        <v>0.0233700201820057</v>
+        <v>0.0310813159510228</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0578777199919018</v>
+        <v>0.07614131523431079</v>
       </c>
       <c r="I114" t="n">
         <v>0.001730378942303</v>
@@ -7210,16 +7210,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L114" t="n">
-        <v>9.23237426331384</v>
+        <v>9.331227237457661</v>
       </c>
       <c r="M114" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N114" t="n">
-        <v>3.110594015930187</v>
+        <v>3.272071426720145</v>
       </c>
       <c r="O114" t="n">
-        <v>5.274201464254571</v>
+        <v>5.406211745310883</v>
       </c>
     </row>
     <row r="115">
@@ -7230,7 +7230,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C115" t="n">
-        <v>6.406616217891267</v>
+        <v>6.754608851072919</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
@@ -7242,10 +7242,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0233700201820057</v>
+        <v>0.0412399121561986</v>
       </c>
       <c r="H115" t="n">
-        <v>0.0578777199919018</v>
+        <v>0.1002011483518324</v>
       </c>
       <c r="I115" t="n">
         <v>0.001730378942303</v>
@@ -7257,16 +7257,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L115" t="n">
-        <v>9.23237426331384</v>
+        <v>9.461452750534528</v>
       </c>
       <c r="M115" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N115" t="n">
-        <v>3.110594015930187</v>
+        <v>3.484796221826993</v>
       </c>
       <c r="O115" t="n">
-        <v>5.274201464254571</v>
+        <v>5.580117555741726</v>
       </c>
     </row>
     <row r="116">
@@ -7277,7 +7277,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C116" t="n">
-        <v>6.406616217891267</v>
+        <v>7.707302147252638</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -7289,10 +7289,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G116" t="n">
-        <v>0.0233700201820057</v>
+        <v>0.0412399121561986</v>
       </c>
       <c r="H116" t="n">
-        <v>0.0578777199919018</v>
+        <v>0.1002011483518324</v>
       </c>
       <c r="I116" t="n">
         <v>0.001730378942303</v>
@@ -7304,16 +7304,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L116" t="n">
-        <v>9.23237426331384</v>
+        <v>11.11260053948062</v>
       </c>
       <c r="M116" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N116" t="n">
-        <v>3.110594015930187</v>
+        <v>3.681614333194319</v>
       </c>
       <c r="O116" t="n">
-        <v>5.274201464254571</v>
+        <v>6.49024699957001</v>
       </c>
     </row>
     <row r="117">
@@ -7324,7 +7324,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C117" t="n">
-        <v>6.406616217891267</v>
+        <v>7.707302147252638</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -7336,10 +7336,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0233700201820057</v>
+        <v>0.0412399121561986</v>
       </c>
       <c r="H117" t="n">
-        <v>0.0578777199919018</v>
+        <v>0.1002011483518324</v>
       </c>
       <c r="I117" t="n">
         <v>0.001730378942303</v>
@@ -7351,16 +7351,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L117" t="n">
-        <v>9.23237426331384</v>
+        <v>11.11260053948062</v>
       </c>
       <c r="M117" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N117" t="n">
-        <v>3.110594015930187</v>
+        <v>3.681614333194319</v>
       </c>
       <c r="O117" t="n">
-        <v>5.274201464254571</v>
+        <v>6.49024699957001</v>
       </c>
     </row>
     <row r="118">
@@ -7371,7 +7371,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C118" t="n">
-        <v>6.406616217891267</v>
+        <v>7.707302147252638</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -7383,10 +7383,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G118" t="n">
-        <v>0.0233700201820057</v>
+        <v>0.0412399121561986</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0578777199919018</v>
+        <v>0.1002011483518324</v>
       </c>
       <c r="I118" t="n">
         <v>0.001730378942303</v>
@@ -7398,16 +7398,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L118" t="n">
-        <v>9.23237426331384</v>
+        <v>11.11260053948062</v>
       </c>
       <c r="M118" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N118" t="n">
-        <v>3.110594015930187</v>
+        <v>3.681614333194319</v>
       </c>
       <c r="O118" t="n">
-        <v>5.274201464254571</v>
+        <v>6.49024699957001</v>
       </c>
     </row>
     <row r="119">
@@ -7418,7 +7418,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C119" t="n">
-        <v>6.406616217891267</v>
+        <v>7.707302147252638</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
@@ -7430,10 +7430,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0233700201820057</v>
+        <v>0.0412399121561986</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0578777199919018</v>
+        <v>0.1002011483518324</v>
       </c>
       <c r="I119" t="n">
         <v>0.001730378942303</v>
@@ -7445,16 +7445,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L119" t="n">
-        <v>9.23237426331384</v>
+        <v>11.11260053948062</v>
       </c>
       <c r="M119" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N119" t="n">
-        <v>3.110594015930187</v>
+        <v>3.681614333194319</v>
       </c>
       <c r="O119" t="n">
-        <v>5.274201464254571</v>
+        <v>6.49024699957001</v>
       </c>
     </row>
     <row r="120">
@@ -7465,7 +7465,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C120" t="n">
-        <v>6.406616217891267</v>
+        <v>7.707302147252638</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
@@ -7477,10 +7477,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0233700201820057</v>
+        <v>0.0412399121561986</v>
       </c>
       <c r="H120" t="n">
-        <v>0.0578777199919018</v>
+        <v>0.1002011483518324</v>
       </c>
       <c r="I120" t="n">
         <v>0.001730378942303</v>
@@ -7492,16 +7492,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L120" t="n">
-        <v>9.23237426331384</v>
+        <v>11.11260053948062</v>
       </c>
       <c r="M120" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N120" t="n">
-        <v>3.110594015930187</v>
+        <v>3.681614333194319</v>
       </c>
       <c r="O120" t="n">
-        <v>5.274201464254571</v>
+        <v>6.49024699957001</v>
       </c>
     </row>
     <row r="121">
@@ -7512,7 +7512,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C121" t="n">
-        <v>6.406616217891267</v>
+        <v>7.707302147252638</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -7524,10 +7524,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G121" t="n">
-        <v>0.0233700201820057</v>
+        <v>0.0412399121561986</v>
       </c>
       <c r="H121" t="n">
-        <v>0.0578777199919018</v>
+        <v>0.1002011483518324</v>
       </c>
       <c r="I121" t="n">
         <v>0.001730378942303</v>
@@ -7539,16 +7539,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L121" t="n">
-        <v>9.23237426331384</v>
+        <v>11.11260053948062</v>
       </c>
       <c r="M121" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N121" t="n">
-        <v>3.110594015930187</v>
+        <v>3.681614333194319</v>
       </c>
       <c r="O121" t="n">
-        <v>5.274201464254571</v>
+        <v>6.49024699957001</v>
       </c>
     </row>
     <row r="122">
@@ -7559,7 +7559,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C122" t="n">
-        <v>6.406616217891267</v>
+        <v>8.284538266944198</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -7571,10 +7571,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0233700201820057</v>
+        <v>0.0412399121561986</v>
       </c>
       <c r="H122" t="n">
-        <v>0.0578777199919018</v>
+        <v>0.1002011483518324</v>
       </c>
       <c r="I122" t="n">
         <v>0.001730378942303</v>
@@ -7586,16 +7586,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L122" t="n">
-        <v>9.23237426331384</v>
+        <v>12.11302968761304</v>
       </c>
       <c r="M122" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N122" t="n">
-        <v>3.110594015930187</v>
+        <v>3.800866272245715</v>
       </c>
       <c r="O122" t="n">
-        <v>5.274201464254571</v>
+        <v>7.041693714561244</v>
       </c>
     </row>
     <row r="123">
@@ -7606,7 +7606,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C123" t="n">
-        <v>6.406616217891267</v>
+        <v>9.193527994932904</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
@@ -7618,10 +7618,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G123" t="n">
-        <v>0.0233700201820057</v>
+        <v>0.0412399121561986</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0578777199919018</v>
+        <v>0.1002011483518324</v>
       </c>
       <c r="I123" t="n">
         <v>0.001730378942303</v>
@@ -7633,16 +7633,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L123" t="n">
-        <v>9.23237426331384</v>
+        <v>13.68843321523493</v>
       </c>
       <c r="M123" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N123" t="n">
-        <v>3.110594015930187</v>
+        <v>3.988655608260197</v>
       </c>
       <c r="O123" t="n">
-        <v>5.274201464254571</v>
+        <v>7.910072151669424</v>
       </c>
     </row>
     <row r="124">
@@ -7653,7 +7653,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C124" t="n">
-        <v>6.406616217891267</v>
+        <v>10.13752301454599</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -7665,10 +7665,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0233700201820057</v>
+        <v>0.0412399121561986</v>
       </c>
       <c r="H124" t="n">
-        <v>0.0578777199919018</v>
+        <v>0.1002011483518324</v>
       </c>
       <c r="I124" t="n">
         <v>0.001730378942303</v>
@@ -7680,16 +7680,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L124" t="n">
-        <v>9.23237426331384</v>
+        <v>15.32450570116564</v>
       </c>
       <c r="M124" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N124" t="n">
-        <v>3.110594015930187</v>
+        <v>4.18367673168517</v>
       </c>
       <c r="O124" t="n">
-        <v>5.274201464254571</v>
+        <v>8.811891935247552</v>
       </c>
     </row>
     <row r="125">
@@ -7700,7 +7700,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C125" t="n">
-        <v>6.406616217891267</v>
+        <v>11.11484634305041</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -7712,10 +7712,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G125" t="n">
-        <v>0.0233700201820057</v>
+        <v>0.0412399121561986</v>
       </c>
       <c r="H125" t="n">
-        <v>0.0578777199919018</v>
+        <v>0.1002011483518324</v>
       </c>
       <c r="I125" t="n">
         <v>0.001730378942303</v>
@@ -7727,16 +7727,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L125" t="n">
-        <v>9.23237426331384</v>
+        <v>17.01834070495587</v>
       </c>
       <c r="M125" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N125" t="n">
-        <v>3.110594015930187</v>
+        <v>4.385583192539684</v>
       </c>
       <c r="O125" t="n">
-        <v>5.274201464254571</v>
+        <v>9.745551005778408</v>
       </c>
     </row>
     <row r="126">
@@ -7747,7 +7747,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C126" t="n">
-        <v>6.406616217891267</v>
+        <v>11.11484634305041</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -7759,10 +7759,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G126" t="n">
-        <v>0.0233700201820057</v>
+        <v>0.0412399121561986</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0578777199919018</v>
+        <v>0.1002011483518324</v>
       </c>
       <c r="I126" t="n">
         <v>0.001730378942303</v>
@@ -7774,16 +7774,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L126" t="n">
-        <v>9.23237426331384</v>
+        <v>17.01834070495587</v>
       </c>
       <c r="M126" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N126" t="n">
-        <v>3.110594015930187</v>
+        <v>4.385583192539684</v>
       </c>
       <c r="O126" t="n">
-        <v>5.274201464254571</v>
+        <v>9.745551005778408</v>
       </c>
     </row>
     <row r="127">
@@ -7794,7 +7794,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C127" t="n">
-        <v>9.364164881881599</v>
+        <v>12.7623589430961</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -7806,10 +7806,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0233700201820057</v>
+        <v>0.0412399121561986</v>
       </c>
       <c r="H127" t="n">
-        <v>0.0578777199919018</v>
+        <v>0.1002011483518324</v>
       </c>
       <c r="I127" t="n">
         <v>0.001730378942303</v>
@@ -7821,16 +7821,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L127" t="n">
-        <v>14.35821062306387</v>
+        <v>19.87370538290057</v>
       </c>
       <c r="M127" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N127" t="n">
-        <v>3.721597729987737</v>
+        <v>4.72594490149171</v>
       </c>
       <c r="O127" t="n">
-        <v>8.099614565665572</v>
+        <v>11.31945703869839</v>
       </c>
     </row>
     <row r="128">
@@ -7841,7 +7841,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C128" t="n">
-        <v>12.84509018312116</v>
+        <v>15.12750927935722</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -7853,10 +7853,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G128" t="n">
-        <v>0.0233700201820057</v>
+        <v>0.0412399121561986</v>
       </c>
       <c r="H128" t="n">
-        <v>0.0578777199919018</v>
+        <v>0.1002011483518324</v>
       </c>
       <c r="I128" t="n">
         <v>0.001730378942303</v>
@@ -7868,16 +7868,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L128" t="n">
-        <v>20.39113028112767</v>
+        <v>23.97283441414544</v>
       </c>
       <c r="M128" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N128" t="n">
-        <v>4.44072648459112</v>
+        <v>5.214564296788574</v>
       </c>
       <c r="O128" t="n">
-        <v>11.42502120086386</v>
+        <v>13.57893862500058</v>
       </c>
     </row>
     <row r="129">
@@ -7888,7 +7888,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C129" t="n">
-        <v>16.32601548436072</v>
+        <v>17.49265961561833</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -7900,10 +7900,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G129" t="n">
-        <v>0.0233700201820057</v>
+        <v>0.0412399121561986</v>
       </c>
       <c r="H129" t="n">
-        <v>0.0578777199919018</v>
+        <v>0.1002011483518324</v>
       </c>
       <c r="I129" t="n">
         <v>0.001730378942303</v>
@@ -7915,16 +7915,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L129" t="n">
-        <v>26.42404993919144</v>
+        <v>28.07196344539029</v>
       </c>
       <c r="M129" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N129" t="n">
-        <v>5.159855239194501</v>
+        <v>5.703183692085435</v>
       </c>
       <c r="O129" t="n">
-        <v>14.75042783606215</v>
+        <v>15.83842021130275</v>
       </c>
     </row>
     <row r="130">
@@ -7935,7 +7935,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C130" t="n">
-        <v>19.80831912757262</v>
+        <v>19.85918829385178</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
@@ -7947,10 +7947,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0233700201820057</v>
+        <v>0.0412399121561986</v>
       </c>
       <c r="H130" t="n">
-        <v>0.0578777199919018</v>
+        <v>0.1002011483518324</v>
       </c>
       <c r="I130" t="n">
         <v>0.001730378942303</v>
@@ -7962,16 +7962,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L130" t="n">
-        <v>32.45935845241897</v>
+        <v>32.17348133179889</v>
       </c>
       <c r="M130" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N130" t="n">
-        <v>5.879268747206878</v>
+        <v>6.192087840791294</v>
       </c>
       <c r="O130" t="n">
-        <v>18.07715123250744</v>
+        <v>18.09921855885194</v>
       </c>
     </row>
     <row r="131">
@@ -7982,7 +7982,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C131" t="n">
-        <v>23.28924442881218</v>
+        <v>22.2243386301129</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -7994,10 +7994,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G131" t="n">
-        <v>0.0233700201820057</v>
+        <v>0.0412399121561986</v>
       </c>
       <c r="H131" t="n">
-        <v>0.0578777199919018</v>
+        <v>0.1002011483518324</v>
       </c>
       <c r="I131" t="n">
         <v>0.001730378942303</v>
@@ -8009,16 +8009,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L131" t="n">
-        <v>38.49227811048275</v>
+        <v>36.27261036304375</v>
       </c>
       <c r="M131" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N131" t="n">
-        <v>6.598397501810261</v>
+        <v>6.680707236088157</v>
       </c>
       <c r="O131" t="n">
-        <v>21.40255786770573</v>
+        <v>20.35870014515413</v>
       </c>
     </row>
     <row r="132">
@@ -8029,7 +8029,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C132" t="n">
-        <v>26.74295570651569</v>
+        <v>24.58948896637401</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -8041,10 +8041,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G132" t="n">
-        <v>0.0233700201820057</v>
+        <v>0.0412399121561986</v>
       </c>
       <c r="H132" t="n">
-        <v>0.0578777199919018</v>
+        <v>0.1002011483518324</v>
       </c>
       <c r="I132" t="n">
         <v>0.001730378942303</v>
@@ -8056,16 +8056,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L132" t="n">
-        <v>44.47803214350218</v>
+        <v>40.37173939428862</v>
       </c>
       <c r="M132" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N132" t="n">
-        <v>7.311904076918363</v>
+        <v>7.169326631385021</v>
       </c>
       <c r="O132" t="n">
-        <v>24.70196633097972</v>
+        <v>22.61818173145631</v>
       </c>
     </row>
     <row r="133">
@@ -8076,7 +8076,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C133" t="n">
-        <v>30.19666698421919</v>
+        <v>26.95463930263512</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -8088,10 +8088,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G133" t="n">
-        <v>0.0233700201820057</v>
+        <v>0.0412399121561986</v>
       </c>
       <c r="H133" t="n">
-        <v>0.0578777199919018</v>
+        <v>0.1002011483518324</v>
       </c>
       <c r="I133" t="n">
         <v>0.001730378942303</v>
@@ -8103,16 +8103,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L133" t="n">
-        <v>50.46378617652161</v>
+        <v>44.47086842553347</v>
       </c>
       <c r="M133" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N133" t="n">
-        <v>8.025410652026466</v>
+        <v>7.657946026681883</v>
       </c>
       <c r="O133" t="n">
-        <v>28.00137479425372</v>
+        <v>24.87766331775849</v>
       </c>
     </row>
     <row r="134">
@@ -8123,7 +8123,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C134" t="n">
-        <v>33.65037826192269</v>
+        <v>29.31978963889623</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G134" t="n">
-        <v>0.0233700201820057</v>
+        <v>0.0412399121561986</v>
       </c>
       <c r="H134" t="n">
-        <v>0.0578777199919018</v>
+        <v>0.1002011483518324</v>
       </c>
       <c r="I134" t="n">
         <v>0.001730378942303</v>
@@ -8150,16 +8150,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L134" t="n">
-        <v>56.44954020954102</v>
+        <v>48.56999745677832</v>
       </c>
       <c r="M134" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N134" t="n">
-        <v>8.738917227134564</v>
+        <v>8.146565421978746</v>
       </c>
       <c r="O134" t="n">
-        <v>31.30078325752771</v>
+        <v>27.13714490406067</v>
       </c>
     </row>
     <row r="135">
@@ -8170,7 +8170,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C135" t="n">
-        <v>37.10408953962619</v>
+        <v>31.68493997515735</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -8182,10 +8182,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G135" t="n">
-        <v>0.0233700201820057</v>
+        <v>0.0412399121561986</v>
       </c>
       <c r="H135" t="n">
-        <v>0.0578777199919018</v>
+        <v>0.1002011483518324</v>
       </c>
       <c r="I135" t="n">
         <v>0.001730378942303</v>
@@ -8197,16 +8197,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L135" t="n">
-        <v>62.43529424256044</v>
+        <v>52.66912648802319</v>
       </c>
       <c r="M135" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N135" t="n">
-        <v>9.452423802242665</v>
+        <v>8.63518481727561</v>
       </c>
       <c r="O135" t="n">
-        <v>34.6001917208017</v>
+        <v>29.39662649036286</v>
       </c>
     </row>
     <row r="136">
@@ -8217,7 +8217,7 @@
         <v>0.0044091386510605</v>
       </c>
       <c r="C136" t="n">
-        <v>40.55780081732968</v>
+        <v>34.05009031141846</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
@@ -8229,10 +8229,10 @@
         <v>0.0030901752534818</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0233700201820057</v>
+        <v>0.0412399121561986</v>
       </c>
       <c r="H136" t="n">
-        <v>0.0578777199919018</v>
+        <v>0.1002011483518324</v>
       </c>
       <c r="I136" t="n">
         <v>0.001730378942303</v>
@@ -8244,16 +8244,16 @@
         <v>0.0014974433154545</v>
       </c>
       <c r="L136" t="n">
-        <v>68.42104827557986</v>
+        <v>56.76825551926805</v>
       </c>
       <c r="M136" t="n">
         <v>0.0008319129530302</v>
       </c>
       <c r="N136" t="n">
-        <v>10.16593037735076</v>
+        <v>9.123804212572471</v>
       </c>
       <c r="O136" t="n">
-        <v>37.89960018407569</v>
+        <v>31.65610807666504</v>
       </c>
     </row>
   </sheetData>
@@ -8512,7 +8512,7 @@
         <v>2025</v>
       </c>
       <c r="B24" t="n">
-        <v>66.2</v>
+        <v>46.3</v>
       </c>
       <c r="C24" t="n">
         <v>70.3</v>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>On Track</t>
+          <t>+19.9</t>
         </is>
       </c>
     </row>
@@ -8595,7 +8595,7 @@
         <v>2030</v>
       </c>
       <c r="B29" t="n">
-        <v>53.3</v>
+        <v>37.3</v>
       </c>
       <c r="C29" t="n">
         <v>59.8</v>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>On Track</t>
+          <t>+16.0</t>
         </is>
       </c>
     </row>
@@ -8678,7 +8678,7 @@
         <v>2035</v>
       </c>
       <c r="B34" t="n">
-        <v>43.5</v>
+        <v>30.4</v>
       </c>
       <c r="C34" t="n">
         <v>50.5</v>
@@ -8688,7 +8688,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>On Track</t>
+          <t>+13.1</t>
         </is>
       </c>
     </row>
@@ -25678,7 +25678,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$18.8</t>
+          <t>$15.1</t>
         </is>
       </c>
     </row>
@@ -27995,7 +27995,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$17.1</t>
+          <t>$14.4</t>
         </is>
       </c>
     </row>
@@ -30312,7 +30312,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$12.2</t>
+          <t>$12.0</t>
         </is>
       </c>
     </row>
@@ -32226,7 +32226,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$10.9</t>
+          <t>$11.0</t>
         </is>
       </c>
     </row>
@@ -34140,7 +34140,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$10.6</t>
+          <t>$10.3</t>
         </is>
       </c>
     </row>
@@ -35806,7 +35806,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$9.5</t>
+          <t>$9.4</t>
         </is>
       </c>
     </row>

--- a/reports/Korea_Petrochemical_NetZero_Report_v2.xlsx
+++ b/reports/Korea_Petrochemical_NetZero_Report_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jinsupark/jinsu-coding/petrochemical_macc_2025/reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{753DD9D8-A174-CC43-A6E2-ECA00F8D9A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD753D9-4ADF-E443-B836-4A0CC9E98E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19880" firstSheet="16" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19880" firstSheet="13" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Executive Summary" sheetId="1" r:id="rId1"/>
@@ -40,6 +40,9 @@
     <sheet name="25. Restructure 40% + NC" sheetId="25" r:id="rId25"/>
     <sheet name="26. Restructure 40% + NC" sheetId="26" r:id="rId26"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'18. Full Facility Database'!$A$4:$J$260</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -18123,6 +18126,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J260"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -18179,7 +18183,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -18211,7 +18215,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2</v>
       </c>
@@ -18243,7 +18247,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>3</v>
       </c>
@@ -18275,7 +18279,7 @@
         <v>2110</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>4</v>
       </c>
@@ -18307,7 +18311,7 @@
         <v>2054</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>5</v>
       </c>
@@ -18339,7 +18343,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>6</v>
       </c>
@@ -18371,7 +18375,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>7</v>
       </c>
@@ -18403,7 +18407,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>8</v>
       </c>
@@ -18435,7 +18439,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>9</v>
       </c>
@@ -18467,7 +18471,7 @@
         <v>2054</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>10</v>
       </c>
@@ -18499,7 +18503,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>11</v>
       </c>
@@ -18531,7 +18535,7 @@
         <v>2110</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>12</v>
       </c>
@@ -18563,7 +18567,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>13</v>
       </c>
@@ -18595,7 +18599,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>14</v>
       </c>
@@ -18627,7 +18631,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>15</v>
       </c>
@@ -18659,7 +18663,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>16</v>
       </c>
@@ -18691,7 +18695,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>17</v>
       </c>
@@ -18723,7 +18727,7 @@
         <v>2054</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>18</v>
       </c>
@@ -18755,7 +18759,7 @@
         <v>2046</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>19</v>
       </c>
@@ -18787,7 +18791,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>20</v>
       </c>
@@ -18819,7 +18823,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>21</v>
       </c>
@@ -18851,7 +18855,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>22</v>
       </c>
@@ -18883,7 +18887,7 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>23</v>
       </c>
@@ -18915,7 +18919,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>24</v>
       </c>
@@ -18947,7 +18951,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>25</v>
       </c>
@@ -18979,7 +18983,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>26</v>
       </c>
@@ -19107,7 +19111,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>30</v>
       </c>
@@ -19139,7 +19143,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>31</v>
       </c>
@@ -19171,7 +19175,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>32</v>
       </c>
@@ -19203,7 +19207,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>33</v>
       </c>
@@ -19235,7 +19239,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>34</v>
       </c>
@@ -19267,7 +19271,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>35</v>
       </c>
@@ -19299,7 +19303,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>36</v>
       </c>
@@ -19331,7 +19335,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>37</v>
       </c>
@@ -19363,7 +19367,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>38</v>
       </c>
@@ -19395,7 +19399,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>39</v>
       </c>
@@ -19427,7 +19431,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>40</v>
       </c>
@@ -19459,7 +19463,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>41</v>
       </c>
@@ -19491,7 +19495,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>42</v>
       </c>
@@ -19523,7 +19527,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>43</v>
       </c>
@@ -19555,7 +19559,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>44</v>
       </c>
@@ -19587,7 +19591,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>45</v>
       </c>
@@ -19619,7 +19623,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>46</v>
       </c>
@@ -19651,7 +19655,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>47</v>
       </c>
@@ -19683,7 +19687,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>48</v>
       </c>
@@ -19715,7 +19719,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>49</v>
       </c>
@@ -19747,7 +19751,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>50</v>
       </c>
@@ -19875,7 +19879,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>54</v>
       </c>
@@ -19907,7 +19911,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>55</v>
       </c>
@@ -19939,7 +19943,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>56</v>
       </c>
@@ -19971,7 +19975,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>57</v>
       </c>
@@ -20003,7 +20007,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>58</v>
       </c>
@@ -20035,7 +20039,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>59</v>
       </c>
@@ -20067,7 +20071,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>60</v>
       </c>
@@ -20099,7 +20103,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>61</v>
       </c>
@@ -20131,7 +20135,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>62</v>
       </c>
@@ -20163,7 +20167,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>63</v>
       </c>
@@ -20195,7 +20199,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>64</v>
       </c>
@@ -20323,7 +20327,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>68</v>
       </c>
@@ -20355,7 +20359,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>69</v>
       </c>
@@ -20387,7 +20391,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>70</v>
       </c>
@@ -20419,7 +20423,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>71</v>
       </c>
@@ -20451,7 +20455,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>72</v>
       </c>
@@ -20483,7 +20487,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>73</v>
       </c>
@@ -20515,7 +20519,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>74</v>
       </c>
@@ -20547,7 +20551,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>75</v>
       </c>
@@ -20579,7 +20583,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>76</v>
       </c>
@@ -20611,7 +20615,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>77</v>
       </c>
@@ -20643,7 +20647,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>78</v>
       </c>
@@ -20771,7 +20775,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>82</v>
       </c>
@@ -20803,7 +20807,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>83</v>
       </c>
@@ -20835,7 +20839,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>84</v>
       </c>
@@ -20867,7 +20871,7 @@
         <v>2058</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>85</v>
       </c>
@@ -20899,7 +20903,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>86</v>
       </c>
@@ -20931,7 +20935,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>87</v>
       </c>
@@ -20963,7 +20967,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>88</v>
       </c>
@@ -20995,7 +20999,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>89</v>
       </c>
@@ -21027,7 +21031,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>90</v>
       </c>
@@ -21059,7 +21063,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>91</v>
       </c>
@@ -21091,7 +21095,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>92</v>
       </c>
@@ -21123,7 +21127,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>93</v>
       </c>
@@ -21155,7 +21159,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>94</v>
       </c>
@@ -21187,7 +21191,7 @@
         <v>2046</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>95</v>
       </c>
@@ -21219,7 +21223,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>96</v>
       </c>
@@ -21251,7 +21255,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>97</v>
       </c>
@@ -21283,7 +21287,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>98</v>
       </c>
@@ -21315,7 +21319,7 @@
         <v>2052</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>99</v>
       </c>
@@ -21347,7 +21351,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>100</v>
       </c>
@@ -21379,7 +21383,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>101</v>
       </c>
@@ -21411,7 +21415,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>102</v>
       </c>
@@ -21443,7 +21447,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>103</v>
       </c>
@@ -21475,7 +21479,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>104</v>
       </c>
@@ -21507,7 +21511,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>105</v>
       </c>
@@ -21539,7 +21543,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>106</v>
       </c>
@@ -21571,7 +21575,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>107</v>
       </c>
@@ -21603,7 +21607,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>108</v>
       </c>
@@ -21635,7 +21639,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>109</v>
       </c>
@@ -21667,7 +21671,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>110</v>
       </c>
@@ -21699,7 +21703,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>111</v>
       </c>
@@ -21731,7 +21735,7 @@
         <v>2059</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>112</v>
       </c>
@@ -21763,7 +21767,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>113</v>
       </c>
@@ -21795,7 +21799,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>114</v>
       </c>
@@ -21827,7 +21831,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>115</v>
       </c>
@@ -21859,7 +21863,7 @@
         <v>2046</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>116</v>
       </c>
@@ -21891,7 +21895,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>117</v>
       </c>
@@ -21923,7 +21927,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>118</v>
       </c>
@@ -21955,7 +21959,7 @@
         <v>2058</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>119</v>
       </c>
@@ -21987,7 +21991,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>120</v>
       </c>
@@ -22019,7 +22023,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>121</v>
       </c>
@@ -22051,7 +22055,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>122</v>
       </c>
@@ -22083,7 +22087,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>123</v>
       </c>
@@ -22211,7 +22215,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>127</v>
       </c>
@@ -22243,7 +22247,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>128</v>
       </c>
@@ -22275,7 +22279,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>129</v>
       </c>
@@ -22307,7 +22311,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>130</v>
       </c>
@@ -22339,7 +22343,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>131</v>
       </c>
@@ -22371,7 +22375,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>132</v>
       </c>
@@ -22403,7 +22407,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>133</v>
       </c>
@@ -22435,7 +22439,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>134</v>
       </c>
@@ -22467,7 +22471,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>135</v>
       </c>
@@ -22499,7 +22503,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>136</v>
       </c>
@@ -22531,7 +22535,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>137</v>
       </c>
@@ -22563,7 +22567,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>138</v>
       </c>
@@ -22595,7 +22599,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>139</v>
       </c>
@@ -22627,7 +22631,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>140</v>
       </c>
@@ -22659,7 +22663,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>141</v>
       </c>
@@ -22787,7 +22791,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>145</v>
       </c>
@@ -22819,7 +22823,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>146</v>
       </c>
@@ -22851,7 +22855,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>147</v>
       </c>
@@ -22883,7 +22887,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>148</v>
       </c>
@@ -22915,7 +22919,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>149</v>
       </c>
@@ -22947,7 +22951,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>150</v>
       </c>
@@ -22979,7 +22983,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>151</v>
       </c>
@@ -23011,7 +23015,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>152</v>
       </c>
@@ -23043,7 +23047,7 @@
         <v>2059</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>153</v>
       </c>
@@ -23075,7 +23079,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>154</v>
       </c>
@@ -23107,7 +23111,7 @@
         <v>2106</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>155</v>
       </c>
@@ -23139,7 +23143,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>156</v>
       </c>
@@ -23171,7 +23175,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>157</v>
       </c>
@@ -23203,7 +23207,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>158</v>
       </c>
@@ -23235,7 +23239,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>159</v>
       </c>
@@ -23267,7 +23271,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>160</v>
       </c>
@@ -23299,7 +23303,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>161</v>
       </c>
@@ -23331,7 +23335,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>162</v>
       </c>
@@ -23363,7 +23367,7 @@
         <v>2046</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>163</v>
       </c>
@@ -23395,7 +23399,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>164</v>
       </c>
@@ -23427,7 +23431,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>165</v>
       </c>
@@ -23459,7 +23463,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>166</v>
       </c>
@@ -23491,7 +23495,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>167</v>
       </c>
@@ -23523,7 +23527,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>168</v>
       </c>
@@ -23555,7 +23559,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>169</v>
       </c>
@@ -23587,7 +23591,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>170</v>
       </c>
@@ -23619,7 +23623,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>171</v>
       </c>
@@ -23651,7 +23655,7 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>172</v>
       </c>
@@ -23683,7 +23687,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>173</v>
       </c>
@@ -23715,7 +23719,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>174</v>
       </c>
@@ -23747,7 +23751,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>175</v>
       </c>
@@ -23779,7 +23783,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>176</v>
       </c>
@@ -23811,7 +23815,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>177</v>
       </c>
@@ -23843,7 +23847,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>178</v>
       </c>
@@ -23875,7 +23879,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>179</v>
       </c>
@@ -23907,7 +23911,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>180</v>
       </c>
@@ -23939,7 +23943,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>181</v>
       </c>
@@ -23971,7 +23975,7 @@
         <v>2054</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>182</v>
       </c>
@@ -24003,7 +24007,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>183</v>
       </c>
@@ -24035,7 +24039,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>184</v>
       </c>
@@ -24067,7 +24071,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>185</v>
       </c>
@@ -24099,7 +24103,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>186</v>
       </c>
@@ -24131,7 +24135,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>187</v>
       </c>
@@ -24163,7 +24167,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>188</v>
       </c>
@@ -24195,7 +24199,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>189</v>
       </c>
@@ -24227,7 +24231,7 @@
         <v>2052</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>190</v>
       </c>
@@ -24259,7 +24263,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>191</v>
       </c>
@@ -24291,7 +24295,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>192</v>
       </c>
@@ -24323,7 +24327,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>193</v>
       </c>
@@ -24355,7 +24359,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>194</v>
       </c>
@@ -24387,7 +24391,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>195</v>
       </c>
@@ -24419,7 +24423,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>196</v>
       </c>
@@ -24451,7 +24455,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>197</v>
       </c>
@@ -24483,7 +24487,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>198</v>
       </c>
@@ -24515,7 +24519,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>199</v>
       </c>
@@ -24547,7 +24551,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>200</v>
       </c>
@@ -24579,7 +24583,7 @@
         <v>2058</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>201</v>
       </c>
@@ -24611,7 +24615,7 @@
         <v>2046</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>202</v>
       </c>
@@ -24643,7 +24647,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>203</v>
       </c>
@@ -24675,7 +24679,7 @@
         <v>2052</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>204</v>
       </c>
@@ -24707,7 +24711,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>205</v>
       </c>
@@ -24739,7 +24743,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>206</v>
       </c>
@@ -24771,7 +24775,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>207</v>
       </c>
@@ -24803,7 +24807,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>208</v>
       </c>
@@ -24835,7 +24839,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>209</v>
       </c>
@@ -24867,7 +24871,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>210</v>
       </c>
@@ -24899,7 +24903,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>211</v>
       </c>
@@ -24931,7 +24935,7 @@
         <v>2058</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>212</v>
       </c>
@@ -24963,7 +24967,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>213</v>
       </c>
@@ -24995,7 +24999,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>214</v>
       </c>
@@ -25027,7 +25031,7 @@
         <v>2058</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>215</v>
       </c>
@@ -25059,7 +25063,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>216</v>
       </c>
@@ -25091,7 +25095,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>217</v>
       </c>
@@ -25123,7 +25127,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>218</v>
       </c>
@@ -25155,7 +25159,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>219</v>
       </c>
@@ -25187,7 +25191,7 @@
         <v>2054</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>220</v>
       </c>
@@ -25219,7 +25223,7 @@
         <v>2059</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>221</v>
       </c>
@@ -25251,7 +25255,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>222</v>
       </c>
@@ -25283,7 +25287,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>223</v>
       </c>
@@ -25315,7 +25319,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>224</v>
       </c>
@@ -25347,7 +25351,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>225</v>
       </c>
@@ -25379,7 +25383,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>226</v>
       </c>
@@ -25411,7 +25415,7 @@
         <v>2052</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>227</v>
       </c>
@@ -25443,7 +25447,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>228</v>
       </c>
@@ -25475,7 +25479,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>229</v>
       </c>
@@ -25507,7 +25511,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>230</v>
       </c>
@@ -25539,7 +25543,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>231</v>
       </c>
@@ -25571,7 +25575,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>232</v>
       </c>
@@ -25603,7 +25607,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>233</v>
       </c>
@@ -25635,7 +25639,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>234</v>
       </c>
@@ -25667,7 +25671,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>235</v>
       </c>
@@ -25699,7 +25703,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>236</v>
       </c>
@@ -25731,7 +25735,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>237</v>
       </c>
@@ -25763,7 +25767,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>238</v>
       </c>
@@ -25795,7 +25799,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>239</v>
       </c>
@@ -25827,7 +25831,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>240</v>
       </c>
@@ -25859,7 +25863,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>241</v>
       </c>
@@ -25891,7 +25895,7 @@
         <v>2058</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>242</v>
       </c>
@@ -25923,7 +25927,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>243</v>
       </c>
@@ -25955,7 +25959,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>244</v>
       </c>
@@ -25987,7 +25991,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>245</v>
       </c>
@@ -26019,7 +26023,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>246</v>
       </c>
@@ -26051,7 +26055,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>247</v>
       </c>
@@ -26083,7 +26087,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>248</v>
       </c>
@@ -26115,7 +26119,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>249</v>
       </c>
@@ -26147,7 +26151,7 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>250</v>
       </c>
@@ -26179,7 +26183,7 @@
         <v>2046</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>251</v>
       </c>
@@ -26211,7 +26215,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>252</v>
       </c>
@@ -26243,7 +26247,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>253</v>
       </c>
@@ -26275,7 +26279,7 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>254</v>
       </c>
@@ -26307,7 +26311,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>255</v>
       </c>
@@ -26339,7 +26343,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>256</v>
       </c>
@@ -26372,6 +26376,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:J260" xr:uid="{00000000-0001-0000-1100-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="S-Oil Shaheen"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
